--- a/DESTINATION-NIGERIA-BRAND-KIT/09_DOCUMENT_TEMPLATES/WORKSHOP_MATERIALS/DN_Action-Plan-Tracker.xlsx
+++ b/DESTINATION-NIGERIA-BRAND-KIT/09_DOCUMENT_TEMPLATES/WORKSHOP_MATERIALS/DN_Action-Plan-Tracker.xlsx
@@ -28,7 +28,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Inter"/>
+      <name val="Public Sans"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
@@ -77,14 +77,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00F3C9B8"/>
+          <fgColor rgb="00E7DFCF"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00F6E2B5"/>
+          <fgColor rgb="00F5F0E6"/>
         </patternFill>
       </fill>
     </dxf>
